--- a/Sample_run/1/student/anlpvhe187047/TC1/GradeDetail.xlsx
+++ b/Sample_run/1/student/anlpvhe187047/TC1/GradeDetail.xlsx
@@ -158,9 +158,6 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN_SENT</x:t>
-  </x:si>
-  <x:si>
     <x:t>PASS</x:t>
   </x:si>
   <x:si>
@@ -170,25 +167,22 @@
     <x:t>Server responding (SYN-ACK)</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN-ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SYN_RECEIVED</x:t>
-  </x:si>
-  <x:si>
     <x:t>(Not validated by this test case)</x:t>
   </x:si>
   <x:si>
     <x:t>ACK</x:t>
   </x:si>
   <x:si>
-    <x:t>ESTABLISHED</x:t>
+    <x:t>Connection established</x:t>
   </x:si>
   <x:si>
     <x:t>INFO</x:t>
   </x:si>
   <x:si>
-    <x:t>PSH-ACK</x:t>
+    <x:t>PSH, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data transfer in progress</x:t>
   </x:si>
   <x:si>
     <x:t>S001</x:t>
@@ -205,10 +199,13 @@
 ]</x:t>
   </x:si>
   <x:si>
-    <x:t>FIN-ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIN_WAIT</x:t>
+    <x:t>FIN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Server closing connection</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Client closing connection</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -926,7 +923,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R11"/>
+  <x:dimension ref="A1:R12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
@@ -940,7 +937,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="10.853482" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="14.139196" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="29.853482" style="0" customWidth="1"/>
@@ -1040,7 +1037,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
         <x:v>44</x:v>
@@ -1052,13 +1049,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>35794</x:v>
+        <x:v>35902</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:18">
@@ -1078,10 +1075,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
         <x:v>48</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>49</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
@@ -1093,10 +1090,10 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
         <x:v>45</x:v>
@@ -1111,10 +1108,10 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>35794</x:v>
+        <x:v>35902</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1122,7 +1119,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>17</x:v>
@@ -1149,10 +1146,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
         <x:v>44</x:v>
@@ -1164,13 +1161,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>35794</x:v>
+        <x:v>35902</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="R4" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:18">
@@ -1178,7 +1175,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>17</x:v>
@@ -1205,7 +1202,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
         <x:v>54</x:v>
@@ -1217,16 +1214,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>35794</x:v>
+        <x:v>35902</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="R5" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:18">
@@ -1234,7 +1231,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>17</x:v>
@@ -1261,10 +1258,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
         <x:v>45</x:v>
@@ -1279,10 +1276,10 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>35794</x:v>
+        <x:v>35902</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1290,7 +1287,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>17</x:v>
@@ -1317,7 +1314,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>54</x:v>
@@ -1329,16 +1326,16 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="O7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P7" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>35794</x:v>
+        <x:v>35902</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1346,7 +1343,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>17</x:v>
@@ -1373,10 +1370,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
         <x:v>44</x:v>
@@ -1388,13 +1385,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>35794</x:v>
+        <x:v>35902</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:18">
@@ -1402,7 +1399,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>17</x:v>
@@ -1429,10 +1426,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
         <x:v>45</x:v>
@@ -1447,10 +1444,10 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>35794</x:v>
+        <x:v>35902</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1458,7 +1455,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>17</x:v>
@@ -1485,10 +1482,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
         <x:v>44</x:v>
@@ -1500,13 +1497,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>35794</x:v>
+        <x:v>35902</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="R10" s="3" t="s">
-        <x:v>55</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:18">
@@ -1514,55 +1511,111 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P11" s="0">
+        <x:v>35902</x:v>
+      </x:c>
+      <x:c r="Q11" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R11" s="3" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="M11" s="0" t="s">
+    </x:row>
+    <x:row r="12" spans="1:18">
+      <x:c r="A12" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="N11" s="0" t="s">
+      <x:c r="N12" s="0" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P11" s="0">
+      <x:c r="O12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P12" s="0">
         <x:v>4000</x:v>
       </x:c>
-      <x:c r="Q11" s="0">
-        <x:v>35794</x:v>
-      </x:c>
-      <x:c r="R11" s="3" t="s">
-        <x:v>55</x:v>
+      <x:c r="Q12" s="0">
+        <x:v>35902</x:v>
+      </x:c>
+      <x:c r="R12" s="3" t="s">
+        <x:v>52</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Sample_run/1/student/anlpvhe187047/TC1/GradeDetail.xlsx
+++ b/Sample_run/1/student/anlpvhe187047/TC1/GradeDetail.xlsx
@@ -1049,7 +1049,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>35902</x:v>
+        <x:v>42890</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1108,7 +1108,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>35902</x:v>
+        <x:v>42890</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1161,7 +1161,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>35902</x:v>
+        <x:v>42890</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1217,7 +1217,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>35902</x:v>
+        <x:v>42890</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1276,7 +1276,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q6" s="0">
-        <x:v>35902</x:v>
+        <x:v>42890</x:v>
       </x:c>
       <x:c r="R6" s="3" t="s">
         <x:v>52</x:v>
@@ -1332,7 +1332,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q7" s="0">
-        <x:v>35902</x:v>
+        <x:v>42890</x:v>
       </x:c>
       <x:c r="R7" s="3" t="s">
         <x:v>52</x:v>
@@ -1385,7 +1385,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P8" s="0">
-        <x:v>35902</x:v>
+        <x:v>42890</x:v>
       </x:c>
       <x:c r="Q8" s="0">
         <x:v>4000</x:v>
@@ -1444,7 +1444,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>35902</x:v>
+        <x:v>42890</x:v>
       </x:c>
       <x:c r="R9" s="3" t="s">
         <x:v>52</x:v>
@@ -1497,7 +1497,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>35902</x:v>
+        <x:v>42890</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1553,7 +1553,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P11" s="0">
-        <x:v>35902</x:v>
+        <x:v>42890</x:v>
       </x:c>
       <x:c r="Q11" s="0">
         <x:v>4000</x:v>
@@ -1612,7 +1612,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q12" s="0">
-        <x:v>35902</x:v>
+        <x:v>42890</x:v>
       </x:c>
       <x:c r="R12" s="3" t="s">
         <x:v>52</x:v>
